--- a/Luban/Config/Datas/Levels/L13/SceneInfo.xlsx
+++ b/Luban/Config/Datas/Levels/L13/SceneInfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1440,7 +1440,7 @@
         <v>13</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>340</v>
+        <v>100</v>
       </c>
       <c r="M4" s="10" t="n">
         <v>12</v>
